--- a/event_registration_forms/030_workshop_attendance_request_form--event_registration_forms.xlsx
+++ b/event_registration_forms/030_workshop_attendance_request_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Workshop Form ID</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,87 +566,87 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>event_start_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>Event Start Date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>attendees_count</t>
+          <t>event_start_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>attendees_count</t>
+          <t>Event Start Time</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>attendee_name</t>
+          <t>event_end_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>attendee_name</t>
+          <t>Event End Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>attendee_email</t>
+          <t>event_end_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>attendee_email</t>
+          <t>Event End Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>attendee_phone</t>
+          <t>event_location</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>attendee_phone</t>
+          <t>Event Location</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,45 +681,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>attendee_address</t>
+          <t>attendee_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>attendee_address</t>
+          <t>Attendee Name</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>attendee_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Additional comments for attendance</t>
-        </is>
-      </c>
+          <t>Attendee Email</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>attendee_phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Attendee Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>attendee_address</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>Attendee Address</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,63 +768,63 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_start_time</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>event_start_time</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>event_end_time</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>event_end_time</t>
+          <t>Confirm Attendance</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>event_location</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>event_location</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -841,50 +837,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>event_name_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Select a tool</t>
-        </is>
-      </c>
+          <t>Event Name 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -896,212 +888,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>event_details</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Additional comments for event</t>
-        </is>
-      </c>
+          <t>Event Details</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>event_name</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>event_name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>event_start_time</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>event_start_time</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>event_end_time</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>event_end_time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>event_location</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>event_location</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>event_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>event_date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Select a tool</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Confirm your attendance</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1118,12 +914,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chatjimmy'}</t>
+          <t>tool_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'chatjimmy'}</t>
+          <t>Tool 1</t>
         </is>
       </c>
     </row>
@@ -1168,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'chatjimmy2'}</t>
+          <t>tool_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'chatjimmy2'}</t>
+          <t>Tool 2</t>
         </is>
       </c>
     </row>
@@ -1185,114 +981,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'chatjimmy3'}</t>
+          <t>tool_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'chatjimmy3'}</t>
+          <t>Tool 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>confirm_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'chatjimmy4'}</t>
+          <t>i_confirm_i_will_attend</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'chatjimmy4'}</t>
+          <t>I confirm I will attend</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>confirm_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'chatjimmy5'}</t>
+          <t>i_will_not_attend</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'chatjimmy5'}</t>
+          <t>I will not attend</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>confirm_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'chatjimmy6'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'chatjimmy6'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>confirm_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'label':_'i_confirm_i_will_attend'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'label': 'I confirm I will attend'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>confirm_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'label':_'i_will_not_attend'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'label': 'I will not attend'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>confirm_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'label':_'maybe'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'label': 'Maybe'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
